--- a/Configs/英雄hero.xlsx
+++ b/Configs/英雄hero.xlsx
@@ -80,7 +80,7 @@
     <t>血量护甲极高，擅长于高频率攻击多个目标，伤害但较低，攻击距离较短</t>
   </si>
   <si>
-    <t>1~500|2~10|113~10000|121~700|131~10000|119~10000|132~3</t>
+    <t>1~2000|2~100|113~10000|121~700|131~10000|119~10000|132~3</t>
   </si>
   <si>
     <t>小小法师</t>
@@ -89,7 +89,7 @@
     <t>蓄力将获得大量技能经验值，单次伤害极高，攻击距离很长</t>
   </si>
   <si>
-    <t>1~500|2~200|121~2500|131~10000|119~10000|132~1</t>
+    <t>1~2000|2~200|121~2500|131~10000|119~10000|132~1</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1171,7 @@
         <v>1000101</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>60</v>
